--- a/资产导入测试.xlsx
+++ b/资产导入测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21710" windowHeight="10520"/>
+    <workbookView windowWidth="29400" windowHeight="12400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>资产编号</t>
   </si>
@@ -46,31 +46,43 @@
     <t>B0001</t>
   </si>
   <si>
+    <t>办公用品1</t>
+  </si>
+  <si>
+    <t>显示屏1</t>
+  </si>
+  <si>
+    <t>B0002</t>
+  </si>
+  <si>
+    <t>办公用品2</t>
+  </si>
+  <si>
+    <t>显示屏2</t>
+  </si>
+  <si>
+    <t>B0003</t>
+  </si>
+  <si>
+    <t>办公用品3</t>
+  </si>
+  <si>
+    <t>显示屏3</t>
+  </si>
+  <si>
+    <t>B0004</t>
+  </si>
+  <si>
+    <t>办公用品4</t>
+  </si>
+  <si>
+    <t>显示屏4</t>
+  </si>
+  <si>
+    <t>B0005</t>
+  </si>
+  <si>
     <t>办公用品</t>
-  </si>
-  <si>
-    <t>显示屏1</t>
-  </si>
-  <si>
-    <t>B0002</t>
-  </si>
-  <si>
-    <t>显示屏2</t>
-  </si>
-  <si>
-    <t>B0003</t>
-  </si>
-  <si>
-    <t>显示屏3</t>
-  </si>
-  <si>
-    <t>B0004</t>
-  </si>
-  <si>
-    <t>显示屏4</t>
-  </si>
-  <si>
-    <t>B0005</t>
   </si>
   <si>
     <t>显示屏5</t>
@@ -1137,7 +1149,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="22.5865384615385" customWidth="1"/>
+    <col min="3" max="3" width="31.8846153846154" customWidth="1"/>
+    <col min="4" max="4" width="17.4615384615385" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -1172,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>1234567</v>
@@ -1183,13 +1200,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>1234567</v>
@@ -1197,13 +1214,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1234567</v>
@@ -1211,13 +1228,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>1234566</v>
@@ -1225,13 +1242,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>1234566</v>
@@ -1239,13 +1256,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>1234566</v>
@@ -1253,13 +1270,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>1234566</v>
@@ -1267,13 +1284,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>1234569</v>
@@ -1281,13 +1298,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>1234569</v>
@@ -1295,13 +1312,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>1234569</v>
@@ -1309,13 +1326,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13">
         <v>1234569</v>
@@ -1323,13 +1340,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>1234569</v>
@@ -1337,13 +1354,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <v>1234569</v>
@@ -1351,13 +1368,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D16">
         <v>1234569</v>
@@ -1365,13 +1382,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D17">
         <v>1234569</v>
@@ -1379,13 +1396,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D18">
         <v>1234569</v>
@@ -1393,13 +1410,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D19">
         <v>1234569</v>
@@ -1407,13 +1424,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D20">
         <v>1234568</v>
@@ -1421,13 +1438,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D21">
         <v>1234568</v>
@@ -1435,13 +1452,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D22">
         <v>1234568</v>
@@ -1449,13 +1466,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>1234568</v>
@@ -1463,13 +1480,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D24">
         <v>1234568</v>
@@ -1477,13 +1494,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D25">
         <v>1234568</v>
@@ -1491,13 +1508,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>1234568</v>
@@ -1505,13 +1522,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D27">
         <v>1234568</v>
@@ -1519,13 +1536,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D28">
         <v>1234568</v>
@@ -1542,7 +1559,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1554,7 +1571,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
